--- a/utils/monday_sprint_sprint_2025-8.xlsx
+++ b/utils/monday_sprint_sprint_2025-8.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="236">
   <si>
     <t>Ticket</t>
   </si>
@@ -514,6 +514,9 @@
   </si>
   <si>
     <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
   </si>
   <si>
     <t>Semana 5</t>
@@ -4218,21 +4221,21 @@
         <v>166</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4244,10 +4247,10 @@
         <v>161</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>19</v>
@@ -4259,7 +4262,7 @@
         <v>165</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>17</v>
@@ -4271,12 +4274,12 @@
         <v>49</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4288,10 +4291,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>24</v>
@@ -4320,7 +4323,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4332,10 +4335,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4353,7 +4356,7 @@
         <v>17</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>21</v>
@@ -4364,7 +4367,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4376,10 +4379,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>24</v>
@@ -4408,7 +4411,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4420,10 +4423,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
@@ -4441,7 +4444,7 @@
         <v>17</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M75" s="2" t="s">
         <v>21</v>
@@ -4452,7 +4455,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4464,10 +4467,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>24</v>
@@ -4496,7 +4499,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4508,10 +4511,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
@@ -4540,7 +4543,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4552,10 +4555,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4584,7 +4587,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -4596,10 +4599,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>24</v>
@@ -4628,7 +4631,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4640,10 +4643,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>19</v>
@@ -4672,7 +4675,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4684,10 +4687,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>19</v>
@@ -4716,7 +4719,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -4728,10 +4731,10 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>24</v>
@@ -4772,10 +4775,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>24</v>
@@ -4804,7 +4807,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -4816,10 +4819,10 @@
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>19</v>
@@ -4848,7 +4851,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -4860,10 +4863,10 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>24</v>
@@ -4892,7 +4895,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -4904,10 +4907,10 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
@@ -4948,10 +4951,10 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>24</v>
@@ -4980,7 +4983,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -4992,10 +4995,10 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>24</v>
@@ -5024,7 +5027,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5036,10 +5039,10 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>19</v>
@@ -5068,7 +5071,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5080,10 +5083,10 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>24</v>
@@ -5112,7 +5115,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5124,10 +5127,10 @@
         <v>17</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>24</v>
@@ -5156,7 +5159,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5168,10 +5171,10 @@
         <v>17</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>24</v>
@@ -5211,23 +5214,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5235,16 +5238,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5263,7 +5266,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5284,7 +5287,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5315,12 +5318,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B2">
         <v>91</v>
@@ -5344,25 +5347,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5379,13 +5382,13 @@
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5417,7 +5420,7 @@
         <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K11">
         <v>91</v>
@@ -5469,13 +5472,13 @@
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -5489,7 +5492,7 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5503,7 +5506,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5511,7 +5514,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5519,7 +5522,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5527,7 +5530,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -5538,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5552,7 +5555,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>162</v>
@@ -5560,16 +5563,16 @@
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">

--- a/utils/monday_sprint_sprint_2025-8.xlsx
+++ b/utils/monday_sprint_sprint_2025-8.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="278">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>30238</t>
+    <t>8874120465</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,13 +87,13 @@
     <t>07/04/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>21/04/2025</t>
   </si>
   <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
+    <t>Não</t>
   </si>
   <si>
     <t>Semana 1</t>
@@ -102,7 +102,7 @@
     <t>Abril</t>
   </si>
   <si>
-    <t>30775</t>
+    <t>8863907728</t>
   </si>
   <si>
     <t>Confirmação de vencimentos - Invoices</t>
@@ -117,16 +117,13 @@
     <t>Feito</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>30963</t>
+    <t>8863809802</t>
   </si>
   <si>
     <t>Listar o Motivo dos Retrabalhos</t>
   </si>
   <si>
-    <t>30977</t>
+    <t>8865648101</t>
   </si>
   <si>
     <t>Correção</t>
@@ -135,7 +132,10 @@
     <t>ERRO: Apontamento Acabamento USE Sequência Inexistente</t>
   </si>
   <si>
-    <t>31022</t>
+    <t>15/04/2025</t>
+  </si>
+  <si>
+    <t>8874866706</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -144,16 +144,25 @@
     <t>QlikSense Controle de Investimentos Dashboard</t>
   </si>
   <si>
-    <t>30979</t>
+    <t>05/07/2025</t>
+  </si>
+  <si>
+    <t>8863663330</t>
   </si>
   <si>
     <t>VPN Telemetria (Web Service)</t>
   </si>
   <si>
+    <t>13/04/2025</t>
+  </si>
+  <si>
+    <t>8874841267</t>
+  </si>
+  <si>
     <t>QlikSense Controle de Investimentos Extração da base</t>
   </si>
   <si>
-    <t>30512</t>
+    <t>8753959850</t>
   </si>
   <si>
     <t>Gráfico no Kg de eletrodo/ton de peça produzida no QlickSense</t>
@@ -162,76 +171,97 @@
     <t>21/03/2025</t>
   </si>
   <si>
+    <t>08/04/2025</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
     <t>Março</t>
   </si>
   <si>
-    <t>30837</t>
+    <t>8864688905</t>
   </si>
   <si>
     <t>Revisar Aplicação QSense - Compara Carteira</t>
   </si>
   <si>
-    <t>30786</t>
+    <t>06/04/2025</t>
+  </si>
+  <si>
+    <t>8864803754</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Itens Comerciais</t>
   </si>
   <si>
-    <t>30852</t>
+    <t>8864239937</t>
   </si>
   <si>
     <t>Relatório para impressão - IROG Usinagem</t>
   </si>
   <si>
-    <t>30966</t>
+    <t>09/04/2025</t>
+  </si>
+  <si>
+    <t>8863692215</t>
   </si>
   <si>
     <t>BOTÃO DE SUBSTITUIÇÃO DE DOCUMENTOS ANEXOS NO CPP</t>
   </si>
   <si>
+    <t>8888369581</t>
+  </si>
+  <si>
     <t>Relatório para impressão - IROG  Ajustagem</t>
   </si>
   <si>
-    <t>08/04/2025</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>30964</t>
+    <t>8863788789</t>
   </si>
   <si>
     <t>Integração do TDM ao sistema Altona</t>
   </si>
   <si>
+    <t>8888370899</t>
+  </si>
+  <si>
     <t>Relatório para impressão - IROG Acabamento</t>
   </si>
   <si>
-    <t>30825</t>
+    <t>8864761182</t>
   </si>
   <si>
     <t>Irog ajustagem</t>
   </si>
   <si>
+    <t>14/04/2025</t>
+  </si>
+  <si>
+    <t>8888372228</t>
+  </si>
+  <si>
     <t>Relatório para impressão - IROG Inspeção</t>
   </si>
   <si>
-    <t>31054</t>
+    <t>8888770658</t>
   </si>
   <si>
     <t>Aparecendo “Erro” na aplicação de FTF no QlikSense</t>
   </si>
   <si>
-    <t>30933</t>
+    <t>8863858568</t>
   </si>
   <si>
     <t>TICKET - PID DE USINAGEM</t>
   </si>
   <si>
-    <t>30376</t>
+    <t>11/04/2025</t>
+  </si>
+  <si>
+    <t>8874162902</t>
   </si>
   <si>
     <t>Criação de BI para verificação de FTF por modelo em aberto</t>
@@ -255,22 +285,19 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>31172</t>
+    <t>8935712116</t>
   </si>
   <si>
     <t>Rateio tempo padrão inspeção</t>
   </si>
   <si>
-    <t>15/04/2025</t>
-  </si>
-  <si>
-    <t>30834</t>
+    <t>8864731770</t>
   </si>
   <si>
     <t>Aplicar filtro no gráfico</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>6631500962</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
@@ -282,7 +309,7 @@
     <t>Maio</t>
   </si>
   <si>
-    <t>30298</t>
+    <t>8648273480</t>
   </si>
   <si>
     <t>Inclusão de informação - Lançamento Refugo</t>
@@ -291,106 +318,118 @@
     <t>07/03/2025</t>
   </si>
   <si>
-    <t>30836</t>
+    <t>20/04/2025</t>
+  </si>
+  <si>
+    <t>8864701794</t>
   </si>
   <si>
     <t>MPO setor ajustagem</t>
   </si>
   <si>
+    <t>8863928921</t>
+  </si>
+  <si>
     <t>Incluir coluna de “Vencimento prorrogaro” e “Motivo da Alteração”.</t>
   </si>
   <si>
-    <t>30849</t>
+    <t>8864579601</t>
   </si>
   <si>
     <t>Tempo padrão rateado</t>
   </si>
   <si>
-    <t>30965</t>
+    <t>8863706652</t>
   </si>
   <si>
     <t>Grupo de recursos da usinagem</t>
   </si>
   <si>
+    <t>10/04/2025</t>
+  </si>
+  <si>
     <t>8584353680</t>
   </si>
   <si>
     <t>Cadastrar a aplicação no Azure</t>
   </si>
   <si>
-    <t>30841</t>
+    <t>8864656063</t>
   </si>
   <si>
     <t>Cadastro CPP</t>
   </si>
   <si>
-    <t>30639</t>
+    <t>8751884914</t>
   </si>
   <si>
     <t>COLUNA N/A CHECKLIST AP119</t>
   </si>
   <si>
-    <t>30915</t>
+    <t>8864071083</t>
   </si>
   <si>
     <t>Inclusão de Campo ComparativoDeposito_Carteira</t>
   </si>
   <si>
-    <t>30982</t>
+    <t>8863636239</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Diferença Estoque de Imobilizado</t>
   </si>
   <si>
-    <t>30997</t>
+    <t>8864035184</t>
   </si>
   <si>
     <t>Integração condição de pagamento Nimbi</t>
   </si>
   <si>
-    <t>31000</t>
+    <t>8865045944</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Consignado - Relatório</t>
   </si>
   <si>
-    <t>30910</t>
+    <t>8864081167</t>
   </si>
   <si>
     <t>Códigos de paradas do sistema</t>
   </si>
   <si>
-    <t>30645</t>
+    <t>8751822973</t>
   </si>
   <si>
     <t>Revisão Checklist Usinagem</t>
   </si>
   <si>
-    <t>30796</t>
+    <t>8864789170</t>
   </si>
   <si>
     <t>Sistema gestão de ações</t>
   </si>
   <si>
-    <t>30999</t>
+    <t>8865063743</t>
   </si>
   <si>
     <t>MELHORIA SISTEMA DE REVISÕES (FLUXO 109)</t>
   </si>
   <si>
-    <t>30756</t>
+    <t>8865001581</t>
   </si>
   <si>
     <t>APONTAMENTO ELETRONICO JATO</t>
   </si>
   <si>
-    <t>30701/29670/31186</t>
+    <t>16/04/2025</t>
+  </si>
+  <si>
+    <t>8751508806</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DE FLUXO 106</t>
   </si>
   <si>
-    <t>30995</t>
+    <t>8865140180</t>
   </si>
   <si>
     <t>UCPC X BENNER - VENCIMENTOS</t>
@@ -405,76 +444,79 @@
     <t>Impedimento</t>
   </si>
   <si>
-    <t>30831</t>
+    <t>8864744275</t>
   </si>
   <si>
     <t>Fiedler</t>
   </si>
   <si>
-    <t>30549</t>
+    <t>8753820640</t>
   </si>
   <si>
     <t>REVISÃO DE FLUXOS 102 E 103 - NOVO SETOR 619</t>
   </si>
   <si>
-    <t>30975</t>
+    <t>8865187697</t>
   </si>
   <si>
     <t>PDI_RespostaNew</t>
   </si>
   <si>
-    <t>30856</t>
+    <t>8864219253</t>
   </si>
   <si>
     <t>Endereçamento do WMS</t>
   </si>
   <si>
-    <t>30158</t>
+    <t>8874275464</t>
   </si>
   <si>
     <t>CADASTRO DE DOCUMENTO NO SETOR 500</t>
   </si>
   <si>
-    <t>30476</t>
+    <t>8754325578</t>
   </si>
   <si>
     <t>Grupo de Etapa LS Carrier</t>
   </si>
   <si>
-    <t>30903</t>
+    <t>8864198476</t>
   </si>
   <si>
     <t>Criação de Sistema de Controle impostos e declarações</t>
   </si>
   <si>
+    <t>8865229657</t>
+  </si>
+  <si>
     <t>Relatório do PDI (PDI_ClientReportPDF_Seq)</t>
   </si>
   <si>
-    <t>30581</t>
+    <t>8874275422</t>
   </si>
   <si>
     <t>INVENTÁRIO INTERMEDIARIO</t>
   </si>
   <si>
-    <t>30360</t>
+    <t>8754462000</t>
   </si>
   <si>
     <t>Alteração do processo de cópia de FTF</t>
   </si>
   <si>
-    <t>27379</t>
+    <t>8754849141</t>
   </si>
   <si>
     <t>Interface Planilhas Custeio Gerencial x Sistema de Custeio - Reunião</t>
   </si>
   <si>
-    <t>30480</t>
+    <t>8754309942</t>
   </si>
   <si>
     <t>Sistemicamente - peças em lote - impossibilidade de retorno ao 8890</t>
   </si>
   <si>
-    <t>30019</t>
+    <t>8540503308</t>
   </si>
   <si>
     <t>Peças em carteira - Ultimo fornecimento +4 anos</t>
@@ -483,7 +525,7 @@
     <t>21/02/2025</t>
   </si>
   <si>
-    <t>30839</t>
+    <t>8864673368</t>
   </si>
   <si>
     <t>Etiqueta amarela</t>
@@ -495,7 +537,7 @@
     <t>Elaborar controle de login automatico a partir do hub no sistema de investimento</t>
   </si>
   <si>
-    <t>30406</t>
+    <t>8875286047</t>
   </si>
   <si>
     <t>Setor 596</t>
@@ -504,49 +546,49 @@
     <t>Implantação</t>
   </si>
   <si>
-    <t>27180</t>
+    <t>8875314500</t>
   </si>
   <si>
     <t>Tempo Padrão Moldagem para IROG</t>
   </si>
   <si>
-    <t>30996</t>
+    <t>8865123848</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Devoluções de estoque</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>8874524204</t>
   </si>
   <si>
     <t>Bloco K Reroativo 2019/01 a 2023/09</t>
   </si>
   <si>
-    <t>31032</t>
+    <t>8877794333</t>
   </si>
   <si>
     <t>Trava C.C 60300</t>
   </si>
   <si>
-    <t>30782</t>
+    <t>8878479216</t>
   </si>
   <si>
     <t>Importar cod. de paradas</t>
   </si>
   <si>
-    <t>31047</t>
+    <t>8888506116</t>
   </si>
   <si>
     <t>Apontamento incorreto</t>
   </si>
   <si>
-    <t>30057</t>
+    <t>8888659610</t>
   </si>
   <si>
     <t>Aplicação Irog</t>
   </si>
   <si>
-    <t>29897</t>
+    <t>8550300602</t>
   </si>
   <si>
     <t>Formulário 596</t>
@@ -558,6 +600,9 @@
     <t>29853</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -585,13 +630,13 @@
     <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
   </si>
   <si>
-    <t>29314</t>
+    <t>8550300625</t>
   </si>
   <si>
     <t>Erro sistema PCP Usinagem ( Erro de comunicação)</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>8874038326</t>
   </si>
   <si>
     <t>Conversão KB18 - Importação de Objetos TRN, PRC e RPT</t>
@@ -600,85 +645,118 @@
     <t>Testes</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>8874229006</t>
   </si>
   <si>
     <t>Revisitar o procedimento de geração das datas, para que gere para todos os patios de uma vez só</t>
   </si>
   <si>
-    <t>31011</t>
+    <t>8865553035</t>
   </si>
   <si>
     <t>Gestão Diário de bordo moldagem - Fast loop Carrosel e ULE</t>
   </si>
   <si>
+    <t>8957137363</t>
+  </si>
+  <si>
     <t>Na tabela YMS1 criar 3 novos atributos para fazer a gravação dos novos campos</t>
   </si>
   <si>
     <t>17/04/2025</t>
   </si>
   <si>
-    <t>25087</t>
+    <t>8874362808</t>
   </si>
   <si>
     <t>Verificar no cadastro do cliente a informação da moeda do cliente</t>
   </si>
   <si>
+    <t>8935545245</t>
+  </si>
+  <si>
     <t>Verificar consulta motivo de parada</t>
   </si>
   <si>
+    <t>8957145534</t>
+  </si>
+  <si>
     <t>Na tela do agendamento, inserir campo para informar transportadora, motorista e volume/quantidade</t>
   </si>
   <si>
+    <t>8874440818</t>
+  </si>
+  <si>
     <t>Visualização faseamento - Criar processo para aplicar a respectiva cotação, mantendo [Informação] para Real e Dolar</t>
   </si>
   <si>
+    <t>8935566067</t>
+  </si>
+  <si>
     <t>Contar 2 entregas para cada registro</t>
   </si>
   <si>
+    <t>8957152568</t>
+  </si>
+  <si>
     <t>Criar triggers no banco de dados após a alteração dos atributos das tabelas</t>
   </si>
   <si>
+    <t>8864159807</t>
+  </si>
+  <si>
     <t>Integração dos dados comerciais Benner</t>
   </si>
   <si>
+    <t>8874362851</t>
+  </si>
+  <si>
     <t>Visualização faseamento - A planilha para importação terá somente abas [Valor Original] e [Peso].</t>
   </si>
   <si>
-    <t>30621</t>
+    <t>8874440992</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Contas para Custos</t>
   </si>
   <si>
+    <t>8874440651</t>
+  </si>
+  <si>
     <t>Cadastro de cotação de moeda</t>
   </si>
   <si>
+    <t>8874441346</t>
+  </si>
+  <si>
     <t>PDI_InstrucaoAnalista</t>
   </si>
   <si>
-    <t>24821</t>
+    <t>8874439714</t>
   </si>
   <si>
     <t>Segregar custeio do macroprocesso (área) Usinagem por Sub-área</t>
   </si>
   <si>
+    <t>8874362893</t>
+  </si>
+  <si>
     <t>Implementar o cadastro para novos registros</t>
   </si>
   <si>
-    <t>26829</t>
+    <t>8874439993</t>
   </si>
   <si>
     <t>Segregar custeio do macroprocesso (área) Fundição por Sub-área</t>
   </si>
   <si>
-    <t>26286</t>
+    <t>8874275358</t>
   </si>
   <si>
     <t>Melhoria Sistema de Custeio - Cadastro Grupo de Clientes</t>
   </si>
   <si>
-    <t>30154</t>
+    <t>8874229095</t>
   </si>
   <si>
     <t>Extração de Roteiros em massa</t>
@@ -690,7 +768,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-8</t>
+    <t>Mai/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1335,7 +1413,7 @@
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1346,22 +1424,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -1382,7 +1460,7 @@
         <v>33</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>27</v>
@@ -1393,22 +1471,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
@@ -1423,13 +1501,13 @@
         <v>32</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>27</v>
@@ -1470,13 +1548,13 @@
         <v>23</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -1487,7 +1565,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1499,10 +1577,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
@@ -1517,13 +1595,13 @@
         <v>32</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1534,7 +1612,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1546,10 +1624,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
@@ -1564,13 +1642,13 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1581,7 +1659,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1593,10 +1671,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>31</v>
@@ -1608,27 +1686,27 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1640,10 +1718,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
@@ -1658,7 +1736,7 @@
         <v>32</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1675,7 +1753,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1687,10 +1765,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>31</v>
@@ -1705,13 +1783,13 @@
         <v>32</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
@@ -1722,7 +1800,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1734,10 +1812,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -1752,13 +1830,13 @@
         <v>32</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>27</v>
@@ -1769,7 +1847,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1781,10 +1859,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
@@ -1799,13 +1877,13 @@
         <v>32</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>27</v>
@@ -1816,7 +1894,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1828,10 +1906,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -1843,19 +1921,19 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1863,7 +1941,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1875,10 +1953,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>31</v>
@@ -1893,13 +1971,13 @@
         <v>32</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>27</v>
@@ -1910,7 +1988,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1922,10 +2000,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>31</v>
@@ -1937,19 +2015,19 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1957,22 +2035,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>31</v>
@@ -1987,13 +2065,13 @@
         <v>32</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>27</v>
@@ -2004,7 +2082,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -2016,34 +2094,34 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -2051,22 +2129,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>31</v>
@@ -2078,19 +2156,19 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -2098,7 +2176,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2110,10 +2188,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>31</v>
@@ -2128,13 +2206,13 @@
         <v>32</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>27</v>
@@ -2145,7 +2223,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2157,10 +2235,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -2175,13 +2253,13 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>27</v>
@@ -2192,22 +2270,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>31</v>
@@ -2219,42 +2297,42 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2266,7 +2344,7 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>24</v>
@@ -2275,10 +2353,10 @@
         <v>33</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -2286,7 +2364,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2298,10 +2376,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>31</v>
@@ -2316,13 +2394,13 @@
         <v>32</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>27</v>
@@ -2333,7 +2411,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2345,10 +2423,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -2360,10 +2438,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2372,15 +2450,15 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2392,10 +2470,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
@@ -2407,27 +2485,27 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2439,10 +2517,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>31</v>
@@ -2457,13 +2535,13 @@
         <v>32</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>27</v>
@@ -2474,7 +2552,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2486,10 +2564,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>31</v>
@@ -2510,7 +2588,7 @@
         <v>33</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>27</v>
@@ -2521,7 +2599,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2533,10 +2611,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2551,13 +2629,13 @@
         <v>32</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>27</v>
@@ -2568,7 +2646,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2580,10 +2658,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>31</v>
@@ -2598,13 +2676,13 @@
         <v>32</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>27</v>
@@ -2615,22 +2693,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>31</v>
@@ -2642,27 +2720,27 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2674,10 +2752,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
@@ -2692,13 +2770,13 @@
         <v>32</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>27</v>
@@ -2709,7 +2787,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2721,10 +2799,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>31</v>
@@ -2736,27 +2814,27 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2768,10 +2846,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>31</v>
@@ -2786,13 +2864,13 @@
         <v>32</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>27</v>
@@ -2803,7 +2881,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2815,10 +2893,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>31</v>
@@ -2833,13 +2911,13 @@
         <v>32</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>27</v>
@@ -2850,7 +2928,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2862,10 +2940,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2880,13 +2958,13 @@
         <v>32</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>27</v>
@@ -2897,7 +2975,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2909,10 +2987,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>31</v>
@@ -2927,13 +3005,13 @@
         <v>32</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -2944,7 +3022,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2956,10 +3034,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>31</v>
@@ -2974,13 +3052,13 @@
         <v>32</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>27</v>
@@ -2991,7 +3069,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -3003,10 +3081,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>31</v>
@@ -3018,27 +3096,27 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -3050,10 +3128,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>31</v>
@@ -3068,13 +3146,13 @@
         <v>32</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>27</v>
@@ -3085,7 +3163,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -3097,10 +3175,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>31</v>
@@ -3115,13 +3193,13 @@
         <v>32</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>27</v>
@@ -3132,7 +3210,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3144,10 +3222,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>31</v>
@@ -3162,13 +3240,13 @@
         <v>32</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>27</v>
@@ -3179,7 +3257,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3191,10 +3269,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>31</v>
@@ -3206,27 +3284,27 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3238,10 +3316,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>31</v>
@@ -3262,7 +3340,7 @@
         <v>33</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>27</v>
@@ -3273,22 +3351,22 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>31</v>
@@ -3300,27 +3378,27 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3332,10 +3410,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>31</v>
@@ -3350,13 +3428,13 @@
         <v>32</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>27</v>
@@ -3367,7 +3445,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3379,10 +3457,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>31</v>
@@ -3394,27 +3472,27 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3426,10 +3504,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>31</v>
@@ -3444,13 +3522,13 @@
         <v>32</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>27</v>
@@ -3461,7 +3539,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3473,10 +3551,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>31</v>
@@ -3491,13 +3569,13 @@
         <v>32</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>27</v>
@@ -3508,7 +3586,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3520,10 +3598,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>31</v>
@@ -3538,13 +3616,13 @@
         <v>23</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>27</v>
@@ -3555,7 +3633,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3567,10 +3645,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>31</v>
@@ -3582,10 +3660,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3594,15 +3672,15 @@
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3614,10 +3692,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>31</v>
@@ -3638,7 +3716,7 @@
         <v>33</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>27</v>
@@ -3649,7 +3727,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3661,10 +3739,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>31</v>
@@ -3679,13 +3757,13 @@
         <v>32</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>27</v>
@@ -3696,7 +3774,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3708,10 +3786,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>31</v>
@@ -3726,13 +3804,13 @@
         <v>23</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>27</v>
@@ -3743,7 +3821,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3755,10 +3833,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>31</v>
@@ -3770,27 +3848,27 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3802,10 +3880,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>31</v>
@@ -3817,27 +3895,27 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3849,10 +3927,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>31</v>
@@ -3864,7 +3942,7 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>24</v>
@@ -3873,18 +3951,18 @@
         <v>33</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3896,10 +3974,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>31</v>
@@ -3911,10 +3989,10 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3923,15 +4001,15 @@
         <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3943,10 +4021,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>31</v>
@@ -3961,10 +4039,10 @@
         <v>32</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>26</v>
@@ -3978,22 +4056,22 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>31</v>
@@ -4005,10 +4083,10 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -4017,15 +4095,15 @@
         <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -4037,10 +4115,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -4055,13 +4133,13 @@
         <v>23</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>27</v>
@@ -4072,7 +4150,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4084,10 +4162,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4108,7 +4186,7 @@
         <v>33</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>27</v>
@@ -4119,7 +4197,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4131,10 +4209,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>31</v>
@@ -4149,13 +4227,13 @@
         <v>32</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>27</v>
@@ -4166,7 +4244,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4178,10 +4256,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>31</v>
@@ -4196,13 +4274,13 @@
         <v>23</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>27</v>
@@ -4213,7 +4291,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4225,10 +4303,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>31</v>
@@ -4243,13 +4321,13 @@
         <v>23</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>27</v>
@@ -4260,7 +4338,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4272,10 +4350,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>31</v>
@@ -4296,7 +4374,7 @@
         <v>33</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>27</v>
@@ -4307,22 +4385,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>31</v>
@@ -4334,19 +4412,19 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>28</v>
@@ -4354,7 +4432,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4366,10 +4444,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>31</v>
@@ -4381,10 +4459,10 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>25</v>
@@ -4393,7 +4471,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>28</v>
@@ -4401,7 +4479,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4413,10 +4491,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4428,57 +4506,57 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>25</v>
@@ -4495,37 +4573,37 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
@@ -4542,7 +4620,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4554,10 +4632,10 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>31</v>
@@ -4569,10 +4647,10 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>25</v>
@@ -4581,15 +4659,15 @@
         <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4601,10 +4679,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4619,10 +4697,10 @@
         <v>23</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>26</v>
@@ -4636,7 +4714,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4648,10 +4726,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>31</v>
@@ -4666,13 +4744,13 @@
         <v>23</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>27</v>
@@ -4683,7 +4761,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4695,10 +4773,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4713,10 +4791,10 @@
         <v>32</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="M75" s="2" t="s">
         <v>26</v>
@@ -4730,7 +4808,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4742,10 +4820,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>31</v>
@@ -4757,19 +4835,19 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>28</v>
@@ -4777,7 +4855,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
@@ -4789,10 +4867,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
@@ -4807,13 +4885,13 @@
         <v>23</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>27</v>
@@ -4824,22 +4902,22 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -4851,19 +4929,19 @@
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>28</v>
@@ -4871,7 +4949,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
@@ -4883,10 +4961,10 @@
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>31</v>
@@ -4898,19 +4976,19 @@
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>28</v>
@@ -4918,7 +4996,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
@@ -4930,10 +5008,10 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -4948,13 +5026,13 @@
         <v>23</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>27</v>
@@ -4965,7 +5043,7 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
@@ -4977,10 +5055,10 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -4992,19 +5070,19 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>28</v>
@@ -5012,7 +5090,7 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
@@ -5024,10 +5102,10 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>31</v>
@@ -5039,19 +5117,19 @@
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>28</v>
@@ -5059,7 +5137,7 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>85</v>
+        <v>229</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
@@ -5071,10 +5149,10 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>31</v>
@@ -5095,7 +5173,7 @@
         <v>33</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>27</v>
@@ -5106,7 +5184,7 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
@@ -5118,10 +5196,10 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5136,13 +5214,13 @@
         <v>23</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>27</v>
@@ -5153,7 +5231,7 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
@@ -5165,10 +5243,10 @@
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>31</v>
@@ -5183,10 +5261,10 @@
         <v>23</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="M85" s="2" t="s">
         <v>26</v>
@@ -5200,7 +5278,7 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
@@ -5212,10 +5290,10 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5230,13 +5308,13 @@
         <v>23</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>27</v>
@@ -5247,22 +5325,22 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>134</v>
+        <v>237</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>31</v>
@@ -5277,13 +5355,13 @@
         <v>23</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>27</v>
@@ -5294,7 +5372,7 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
@@ -5306,10 +5384,10 @@
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>31</v>
@@ -5324,10 +5402,10 @@
         <v>23</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>26</v>
@@ -5341,7 +5419,7 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
@@ -5353,10 +5431,10 @@
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
@@ -5371,13 +5449,13 @@
         <v>23</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>27</v>
@@ -5388,7 +5466,7 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>16</v>
@@ -5400,10 +5478,10 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>31</v>
@@ -5418,10 +5496,10 @@
         <v>23</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>26</v>
@@ -5435,7 +5513,7 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>16</v>
@@ -5447,10 +5525,10 @@
         <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>31</v>
@@ -5465,13 +5543,13 @@
         <v>23</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>27</v>
@@ -5482,7 +5560,7 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>16</v>
@@ -5494,10 +5572,10 @@
         <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>31</v>
@@ -5512,7 +5590,7 @@
         <v>23</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>25</v>
@@ -5540,23 +5618,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="E2" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5564,16 +5642,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5584,15 +5662,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>14.15</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5605,7 +5683,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -5613,7 +5691,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5644,12 +5722,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="B2">
         <v>91</v>
@@ -5663,35 +5741,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5699,7 +5777,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -5708,13 +5786,13 @@
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5729,10 +5807,16 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
       <c r="D11" t="s">
         <v>41</v>
       </c>
@@ -5746,10 +5830,10 @@
         <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K11">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="M11" t="s">
         <v>25</v>
@@ -5758,15 +5842,15 @@
         <v>11</v>
       </c>
       <c r="P11" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -5778,59 +5862,53 @@
         <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="K12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="P12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Q12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -5838,7 +5916,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5846,7 +5924,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5854,7 +5932,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5862,10 +5940,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5873,7 +5951,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5881,142 +5959,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>46</v>
+        <v>170</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>189</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>56</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>194</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>58</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
